--- a/TimeTracking.xlsx
+++ b/TimeTracking.xlsx
@@ -1,24 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="17830"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silva\Desktop\ProjectStone\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aaron\Desktop\Capstone\GitCap\MillerConstruction-\MillerConstruction-\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4575" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15348" windowHeight="4572" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027" concurrentCalc="0"/>
+  <calcPr calcId="152511" concurrentCalc="0"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
-      <x14:workbookPr defaultImageDpi="32767"/>
-    </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
     </ext>
@@ -62,9 +59,6 @@
     <t>Members</t>
   </si>
   <si>
-    <t>Name 2</t>
-  </si>
-  <si>
     <t>Name 3</t>
   </si>
   <si>
@@ -81,12 +75,15 @@
   </si>
   <si>
     <t>Joel Silva</t>
+  </si>
+  <si>
+    <t>Aaron O</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -399,57 +396,57 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
       <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" t="s">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
       <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
         <v>14</v>
       </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
       <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" t="s">
         <v>14</v>
       </c>
-      <c r="H3" t="s">
-        <v>15</v>
-      </c>
       <c r="I3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -460,9 +457,12 @@
         <f>B4</f>
         <v>11</v>
       </c>
+      <c r="D4">
+        <v>11</v>
+      </c>
       <c r="E4">
         <f>D4</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <f>F4</f>
@@ -473,7 +473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -483,7 +483,7 @@
       </c>
       <c r="E5">
         <f>D5+E4</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <f t="shared" ref="G5:G13" si="0">F5</f>
@@ -494,7 +494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -504,7 +504,7 @@
       </c>
       <c r="E6">
         <f t="shared" ref="E6:E13" si="3">D6+E5</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
@@ -515,7 +515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -525,7 +525,7 @@
       </c>
       <c r="E7">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <f t="shared" si="0"/>
@@ -536,7 +536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -546,7 +546,7 @@
       </c>
       <c r="E8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <f t="shared" si="0"/>
@@ -557,7 +557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -567,7 +567,7 @@
       </c>
       <c r="E9">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <f t="shared" si="0"/>
@@ -578,7 +578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -588,7 +588,7 @@
       </c>
       <c r="E10">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G10">
         <f t="shared" si="0"/>
@@ -599,7 +599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -609,7 +609,7 @@
       </c>
       <c r="E11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G11">
         <f t="shared" si="0"/>
@@ -620,7 +620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -630,7 +630,7 @@
       </c>
       <c r="E12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G12">
         <f t="shared" si="0"/>
@@ -641,7 +641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -651,7 +651,7 @@
       </c>
       <c r="E13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G13">
         <f t="shared" si="0"/>
